--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_B_SPAT-CSTD-A0-01-B-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_B_SPAT-CSTD-A0-01-B-C0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_JPlaptop\BEV_MCU\git_v043_AlertFix\src\PE1VM1\App\MET\IpcApplication\Vom\Alert\matrix\scc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\ソフトチーム\20260106_REMWAR_RW\045\IpcApplication\Vom\Alert\matrix\scc\ref更新\IpcApplication\Vom\Alert\matrix\scc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66947DF2-68BC-4A2E-B40C-A2CD218090A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C07E45F2-7FB7-4606-87EA-F2E1A9A180DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14265" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2910" yWindow="1050" windowWidth="22740" windowHeight="14070" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙（承認欄）" sheetId="12" r:id="rId1"/>
@@ -675,7 +675,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2508" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2510" uniqueCount="286">
   <si>
     <t>更新履歴</t>
     <phoneticPr fontId="2"/>
@@ -3100,6 +3100,25 @@
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>RWの削除
+[Reference]シート
+RW記載を対象外に変更</t>
+    <rPh sb="23" eb="25">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>タイショウガイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1.2.0</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -4508,7 +4527,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="291">
+  <cellXfs count="295">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5175,19 +5194,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5238,37 +5245,16 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5313,10 +5299,31 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5370,27 +5377,37 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 3 3 4 3" xfId="2" xr:uid="{8A7CCA27-417A-42B6-88EE-9DC1794F3ADA}"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill>
@@ -10417,6 +10434,188 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>69273</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>2</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34610404-A84C-43A2-B1B1-EE2AB8B3E9BD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16452273" y="5541820"/>
+          <a:ext cx="22098000" cy="1039089"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>692726</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>77</xdr:col>
+      <xdr:colOff>683200</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="正方形/長方形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5BDC2DB-8BC5-40D5-9AA1-FAF75F21BFD2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="31622999" y="6580909"/>
+          <a:ext cx="25621383" cy="4502727"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -21573,10 +21772,10 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="C1:AM57"/>
-  <sheetFormatPr defaultColWidth="8.08984375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.125" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="52" width="2.08984375" style="198" customWidth="1"/>
-    <col min="53" max="16384" width="8.08984375" style="198"/>
+    <col min="1" max="52" width="2.125" style="198" customWidth="1"/>
+    <col min="53" max="16384" width="8.125" style="198"/>
   </cols>
   <sheetData>
     <row r="1" spans="6:20" ht="13.15" customHeight="1"/>
@@ -21639,27 +21838,27 @@
       </c>
     </row>
     <row r="35" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y35" s="229" t="s">
+      <c r="Y35" s="225" t="s">
         <v>233</v>
       </c>
-      <c r="Z35" s="230"/>
-      <c r="AA35" s="230"/>
-      <c r="AB35" s="230"/>
-      <c r="AC35" s="231"/>
-      <c r="AD35" s="229" t="s">
+      <c r="Z35" s="226"/>
+      <c r="AA35" s="226"/>
+      <c r="AB35" s="226"/>
+      <c r="AC35" s="227"/>
+      <c r="AD35" s="225" t="s">
         <v>234</v>
       </c>
-      <c r="AE35" s="230"/>
-      <c r="AF35" s="230"/>
-      <c r="AG35" s="230"/>
-      <c r="AH35" s="231"/>
-      <c r="AI35" s="229" t="s">
+      <c r="AE35" s="226"/>
+      <c r="AF35" s="226"/>
+      <c r="AG35" s="226"/>
+      <c r="AH35" s="227"/>
+      <c r="AI35" s="225" t="s">
         <v>235</v>
       </c>
-      <c r="AJ35" s="230"/>
-      <c r="AK35" s="230"/>
-      <c r="AL35" s="230"/>
-      <c r="AM35" s="231"/>
+      <c r="AJ35" s="226"/>
+      <c r="AK35" s="226"/>
+      <c r="AL35" s="226"/>
+      <c r="AM35" s="227"/>
     </row>
     <row r="36" spans="3:39" ht="13.15" customHeight="1">
       <c r="D36" s="202"/>
@@ -21758,27 +21957,27 @@
       </c>
     </row>
     <row r="43" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y43" s="229" t="s">
+      <c r="Y43" s="225" t="s">
         <v>233</v>
       </c>
-      <c r="Z43" s="230"/>
-      <c r="AA43" s="230"/>
-      <c r="AB43" s="230"/>
-      <c r="AC43" s="231"/>
-      <c r="AD43" s="229" t="s">
+      <c r="Z43" s="226"/>
+      <c r="AA43" s="226"/>
+      <c r="AB43" s="226"/>
+      <c r="AC43" s="227"/>
+      <c r="AD43" s="225" t="s">
         <v>234</v>
       </c>
-      <c r="AE43" s="230"/>
-      <c r="AF43" s="230"/>
-      <c r="AG43" s="230"/>
-      <c r="AH43" s="231"/>
-      <c r="AI43" s="229" t="s">
+      <c r="AE43" s="226"/>
+      <c r="AF43" s="226"/>
+      <c r="AG43" s="226"/>
+      <c r="AH43" s="227"/>
+      <c r="AI43" s="225" t="s">
         <v>235</v>
       </c>
-      <c r="AJ43" s="230"/>
-      <c r="AK43" s="230"/>
-      <c r="AL43" s="230"/>
-      <c r="AM43" s="231"/>
+      <c r="AJ43" s="226"/>
+      <c r="AK43" s="226"/>
+      <c r="AL43" s="226"/>
+      <c r="AM43" s="227"/>
     </row>
     <row r="44" spans="3:39" ht="13.15" customHeight="1">
       <c r="D44" s="202"/>
@@ -21876,27 +22075,27 @@
       </c>
     </row>
     <row r="51" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y51" s="229" t="s">
+      <c r="Y51" s="225" t="s">
         <v>233</v>
       </c>
-      <c r="Z51" s="230"/>
-      <c r="AA51" s="230"/>
-      <c r="AB51" s="230"/>
-      <c r="AC51" s="231"/>
-      <c r="AD51" s="229" t="s">
+      <c r="Z51" s="226"/>
+      <c r="AA51" s="226"/>
+      <c r="AB51" s="226"/>
+      <c r="AC51" s="227"/>
+      <c r="AD51" s="225" t="s">
         <v>234</v>
       </c>
-      <c r="AE51" s="230"/>
-      <c r="AF51" s="230"/>
-      <c r="AG51" s="230"/>
-      <c r="AH51" s="231"/>
-      <c r="AI51" s="229" t="s">
+      <c r="AE51" s="226"/>
+      <c r="AF51" s="226"/>
+      <c r="AG51" s="226"/>
+      <c r="AH51" s="227"/>
+      <c r="AI51" s="225" t="s">
         <v>235</v>
       </c>
-      <c r="AJ51" s="230"/>
-      <c r="AK51" s="230"/>
-      <c r="AL51" s="230"/>
-      <c r="AM51" s="231"/>
+      <c r="AJ51" s="226"/>
+      <c r="AK51" s="226"/>
+      <c r="AL51" s="226"/>
+      <c r="AM51" s="227"/>
     </row>
     <row r="52" spans="4:39" ht="13.15" customHeight="1">
       <c r="D52" s="202"/>
@@ -22013,16 +22212,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:X13"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="4.453125" customWidth="1"/>
+    <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="9" style="10" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="69.453125" customWidth="1"/>
-    <col min="5" max="6" width="12.7265625" customWidth="1"/>
-    <col min="7" max="18" width="13.08984375" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="69.5" customWidth="1"/>
+    <col min="5" max="6" width="12.75" customWidth="1"/>
+    <col min="7" max="18" width="13.125" hidden="1" customWidth="1"/>
     <col min="19" max="22" width="0" hidden="1" customWidth="1"/>
-    <col min="23" max="23" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:24" ht="25.5" customHeight="1">
@@ -22033,18 +22232,18 @@
       <c r="H2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="232" t="s">
+      <c r="I2" s="228" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
-      <c r="M2" s="232"/>
-      <c r="N2" s="232"/>
-      <c r="O2" s="232"/>
-      <c r="P2" s="232"/>
-      <c r="Q2" s="232"/>
-      <c r="R2" s="232"/>
+      <c r="J2" s="228"/>
+      <c r="K2" s="228"/>
+      <c r="L2" s="228"/>
+      <c r="M2" s="228"/>
+      <c r="N2" s="228"/>
+      <c r="O2" s="228"/>
+      <c r="P2" s="228"/>
+      <c r="Q2" s="228"/>
+      <c r="R2" s="228"/>
     </row>
     <row r="3" spans="2:24" ht="25.5" customHeight="1">
       <c r="C3" s="7"/>
@@ -22057,25 +22256,25 @@
       <c r="H3" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="I3" s="233" t="s">
+      <c r="I3" s="229" t="s">
         <v>197</v>
       </c>
-      <c r="J3" s="234"/>
-      <c r="K3" s="234"/>
-      <c r="L3" s="234"/>
-      <c r="M3" s="234"/>
-      <c r="N3" s="234"/>
-      <c r="O3" s="234"/>
-      <c r="P3" s="234"/>
-      <c r="Q3" s="234"/>
-      <c r="R3" s="234"/>
+      <c r="J3" s="230"/>
+      <c r="K3" s="230"/>
+      <c r="L3" s="230"/>
+      <c r="M3" s="230"/>
+      <c r="N3" s="230"/>
+      <c r="O3" s="230"/>
+      <c r="P3" s="230"/>
+      <c r="Q3" s="230"/>
+      <c r="R3" s="230"/>
     </row>
     <row r="4" spans="2:24" ht="25.5" customHeight="1">
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
       <c r="E4" s="24" t="str">
         <f>DGET(B8:C14,"Ver.",H4:H5)</f>
-        <v>1.1.1</v>
+        <v>1.2.0</v>
       </c>
       <c r="F4" s="7"/>
       <c r="H4" s="10" t="s">
@@ -22089,45 +22288,45 @@
       <c r="F5" s="7"/>
       <c r="H5" s="12">
         <f>MAX(B9:B14)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:24" ht="13.5" thickBot="1"/>
+    <row r="6" spans="2:24" ht="14.25" thickBot="1"/>
     <row r="7" spans="2:24">
-      <c r="C7" s="237" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="238"/>
-      <c r="E7" s="239" t="s">
+      <c r="C7" s="233" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="234"/>
+      <c r="E7" s="235" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="239"/>
-      <c r="G7" s="240" t="s">
+      <c r="F7" s="235"/>
+      <c r="G7" s="236" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="240"/>
-      <c r="I7" s="240"/>
-      <c r="J7" s="240"/>
-      <c r="K7" s="240"/>
-      <c r="L7" s="240"/>
-      <c r="M7" s="241" t="s">
+      <c r="H7" s="236"/>
+      <c r="I7" s="236"/>
+      <c r="J7" s="236"/>
+      <c r="K7" s="236"/>
+      <c r="L7" s="236"/>
+      <c r="M7" s="237" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="241"/>
-      <c r="O7" s="241"/>
-      <c r="P7" s="241"/>
-      <c r="Q7" s="241"/>
-      <c r="R7" s="242"/>
-      <c r="S7" s="235" t="s">
+      <c r="N7" s="237"/>
+      <c r="O7" s="237"/>
+      <c r="P7" s="237"/>
+      <c r="Q7" s="237"/>
+      <c r="R7" s="238"/>
+      <c r="S7" s="231" t="s">
         <v>229</v>
       </c>
-      <c r="T7" s="235"/>
-      <c r="U7" s="235"/>
-      <c r="V7" s="235"/>
-      <c r="W7" s="235"/>
-      <c r="X7" s="236"/>
+      <c r="T7" s="231"/>
+      <c r="U7" s="231"/>
+      <c r="V7" s="231"/>
+      <c r="W7" s="231"/>
+      <c r="X7" s="232"/>
     </row>
-    <row r="8" spans="2:24" ht="26.5" thickBot="1">
+    <row r="8" spans="2:24" ht="27.75" thickBot="1">
       <c r="B8" s="10" t="s">
         <v>98</v>
       </c>
@@ -22198,7 +22397,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:24" ht="13.5" thickTop="1">
+    <row r="9" spans="2:24" ht="14.25" thickTop="1">
       <c r="B9" s="10">
         <f>IF(C9=0,0,ROW()-ROW($B$8))</f>
         <v>1</v>
@@ -22250,7 +22449,7 @@
         <v>45281</v>
       </c>
     </row>
-    <row r="10" spans="2:24" ht="91">
+    <row r="10" spans="2:24" ht="94.5">
       <c r="B10" s="10">
         <f t="shared" ref="B10:B13" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
         <v>2</v>
@@ -22290,53 +22489,57 @@
         <v>45371</v>
       </c>
     </row>
-    <row r="11" spans="2:24" ht="91">
+    <row r="11" spans="2:24" ht="94.5">
       <c r="B11" s="10">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C11" s="226" t="s">
+      <c r="C11" s="288" t="s">
         <v>280</v>
       </c>
-      <c r="D11" s="224" t="s">
+      <c r="D11" s="289" t="s">
         <v>283</v>
       </c>
-      <c r="E11" s="225" t="s">
+      <c r="E11" s="290" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="225" t="s">
+      <c r="F11" s="290" t="s">
         <v>32</v>
       </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="29"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="1"/>
-      <c r="W11" s="227" t="s">
+      <c r="G11" s="291"/>
+      <c r="H11" s="291"/>
+      <c r="I11" s="291"/>
+      <c r="J11" s="291"/>
+      <c r="K11" s="291"/>
+      <c r="L11" s="291"/>
+      <c r="M11" s="291"/>
+      <c r="N11" s="291"/>
+      <c r="O11" s="291"/>
+      <c r="P11" s="291"/>
+      <c r="Q11" s="291"/>
+      <c r="R11" s="292"/>
+      <c r="S11" s="291"/>
+      <c r="T11" s="291"/>
+      <c r="U11" s="291"/>
+      <c r="V11" s="291"/>
+      <c r="W11" s="293" t="s">
         <v>231</v>
       </c>
-      <c r="X11" s="228">
+      <c r="X11" s="294">
         <v>46008</v>
       </c>
     </row>
-    <row r="12" spans="2:24">
+    <row r="12" spans="2:24" ht="40.5">
       <c r="B12" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="C12" s="224" t="s">
+        <v>285</v>
+      </c>
+      <c r="D12" s="287" t="s">
+        <v>284</v>
+      </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -22358,7 +22561,7 @@
       <c r="W12" s="1"/>
       <c r="X12" s="3"/>
     </row>
-    <row r="13" spans="2:24" ht="13.5" thickBot="1">
+    <row r="13" spans="2:24" ht="14.25" thickBot="1">
       <c r="B13" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -22409,11 +22612,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:E39"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="4.6328125" customWidth="1"/>
-    <col min="3" max="3" width="3.453125" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" customWidth="1"/>
+    <col min="2" max="2" width="4.625" customWidth="1"/>
+    <col min="3" max="3" width="3.5" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
     <col min="5" max="5" width="106" customWidth="1"/>
   </cols>
   <sheetData>
@@ -22427,13 +22630,13 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="13.5" thickBot="1">
+    <row r="6" spans="2:5" ht="14.25" thickBot="1">
       <c r="B6" s="156" t="s">
         <v>141</v>
       </c>
       <c r="C6" s="156"/>
     </row>
-    <row r="7" spans="2:5" ht="13.5" thickBot="1">
+    <row r="7" spans="2:5" ht="14.25" thickBot="1">
       <c r="C7" s="82" t="s">
         <v>143</v>
       </c>
@@ -22458,7 +22661,7 @@
       <c r="D9" s="167"/>
       <c r="E9" s="166"/>
     </row>
-    <row r="10" spans="2:5" ht="13.5" thickBot="1">
+    <row r="10" spans="2:5" ht="14.25" thickBot="1">
       <c r="C10" s="163"/>
       <c r="D10" s="93"/>
       <c r="E10" s="6"/>
@@ -22466,14 +22669,14 @@
     <row r="11" spans="2:5">
       <c r="C11" s="161"/>
     </row>
-    <row r="12" spans="2:5" ht="13.5" thickBot="1">
+    <row r="12" spans="2:5" ht="14.25" thickBot="1">
       <c r="B12" s="156" t="s">
         <v>142</v>
       </c>
       <c r="C12" s="89"/>
       <c r="D12" s="89"/>
     </row>
-    <row r="13" spans="2:5" ht="13.5" thickBot="1">
+    <row r="13" spans="2:5" ht="14.25" thickBot="1">
       <c r="B13" s="157"/>
       <c r="C13" s="162" t="s">
         <v>143</v>
@@ -22485,7 +22688,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="13.5" thickTop="1">
+    <row r="14" spans="2:5" ht="14.25" thickTop="1">
       <c r="C14" s="159">
         <v>0</v>
       </c>
@@ -22562,17 +22765,17 @@
         <v>191</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="13.5" thickBot="1">
+    <row r="21" spans="2:5" ht="14.25" thickBot="1">
       <c r="C21" s="163"/>
       <c r="D21" s="93"/>
       <c r="E21" s="6"/>
     </row>
-    <row r="24" spans="2:5" ht="13.5" thickBot="1">
+    <row r="24" spans="2:5" ht="14.25" thickBot="1">
       <c r="B24" s="156" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="13.5" thickBot="1">
+    <row r="25" spans="2:5" ht="14.25" thickBot="1">
       <c r="C25" s="162" t="s">
         <v>143</v>
       </c>
@@ -22659,26 +22862,26 @@
       <c r="D33" s="92"/>
       <c r="E33" s="3"/>
     </row>
-    <row r="34" spans="2:5" ht="13.5" thickBot="1">
+    <row r="34" spans="2:5" ht="14.25" thickBot="1">
       <c r="C34" s="163"/>
       <c r="D34" s="93"/>
       <c r="E34" s="6"/>
     </row>
-    <row r="37" spans="2:5" ht="13.5" thickBot="1">
+    <row r="37" spans="2:5" ht="14.25" thickBot="1">
       <c r="B37" s="156" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="38" spans="2:5">
-      <c r="C38" s="243"/>
-      <c r="D38" s="244"/>
+      <c r="C38" s="239"/>
+      <c r="D38" s="240"/>
       <c r="E38" s="115" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="13.5" thickBot="1">
-      <c r="C39" s="245"/>
-      <c r="D39" s="246"/>
+    <row r="39" spans="2:5" ht="14.25" thickBot="1">
+      <c r="C39" s="241"/>
+      <c r="D39" s="242"/>
       <c r="E39" s="6" t="s">
         <v>130</v>
       </c>
@@ -22703,131 +22906,131 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:N37"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="26.7265625" customWidth="1"/>
-    <col min="9" max="9" width="20.90625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="26.75" customWidth="1"/>
+    <col min="9" max="9" width="20.875" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="13.5" thickBot="1"/>
+    <row r="1" spans="2:14" ht="14.25" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="272" t="s">
+      <c r="B2" s="243" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="273"/>
-      <c r="D2" s="260" t="s">
+      <c r="C2" s="244"/>
+      <c r="D2" s="249" t="s">
         <v>246</v>
       </c>
-      <c r="E2" s="261"/>
-      <c r="F2" s="261"/>
-      <c r="G2" s="261"/>
-      <c r="H2" s="262"/>
+      <c r="E2" s="250"/>
+      <c r="F2" s="250"/>
+      <c r="G2" s="250"/>
+      <c r="H2" s="251"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="247" t="s">
+      <c r="B3" s="245" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="248"/>
-      <c r="D3" s="263" t="s">
+      <c r="C3" s="246"/>
+      <c r="D3" s="252" t="s">
         <v>273</v>
       </c>
-      <c r="E3" s="264"/>
-      <c r="F3" s="264"/>
-      <c r="G3" s="264"/>
-      <c r="H3" s="265"/>
+      <c r="E3" s="253"/>
+      <c r="F3" s="253"/>
+      <c r="G3" s="253"/>
+      <c r="H3" s="254"/>
     </row>
-    <row r="4" spans="2:14" ht="13.5" thickBot="1">
-      <c r="B4" s="258" t="s">
+    <row r="4" spans="2:14" ht="14.25" thickBot="1">
+      <c r="B4" s="247" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="259"/>
-      <c r="D4" s="266" t="str">
+      <c r="C4" s="248"/>
+      <c r="D4" s="255" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_B_SPAT-CSTD-A0-01-B-C0.c</v>
       </c>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="268"/>
+      <c r="E4" s="256"/>
+      <c r="F4" s="256"/>
+      <c r="G4" s="256"/>
+      <c r="H4" s="257"/>
     </row>
-    <row r="5" spans="2:14" ht="13.5" thickBot="1">
+    <row r="5" spans="2:14" ht="14.25" thickBot="1">
       <c r="D5" t="str">
         <f ca="1">IF(LEN(表紙!D3&amp;".c") = LENB(表紙!D3&amp;".c"),"※モジュール名 全角チェックOK","※モジュール名 全角チェックNG：ファイル名に全角文字が使用されています！")</f>
         <v>※モジュール名 全角チェックOK</v>
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="272" t="s">
+      <c r="B6" s="243" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="273"/>
-      <c r="D6" s="269" t="str">
+      <c r="C6" s="244"/>
+      <c r="D6" s="258" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>B_SPAT</v>
       </c>
-      <c r="E6" s="270"/>
-      <c r="F6" s="270"/>
-      <c r="G6" s="270"/>
-      <c r="H6" s="271"/>
+      <c r="E6" s="259"/>
+      <c r="F6" s="259"/>
+      <c r="G6" s="259"/>
+      <c r="H6" s="260"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="247" t="s">
+      <c r="B7" s="245" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="248"/>
-      <c r="D7" s="249">
+      <c r="C7" s="246"/>
+      <c r="D7" s="261">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="250"/>
-      <c r="F7" s="250"/>
-      <c r="G7" s="250"/>
-      <c r="H7" s="251"/>
+      <c r="E7" s="262"/>
+      <c r="F7" s="262"/>
+      <c r="G7" s="262"/>
+      <c r="H7" s="263"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="247" t="s">
+      <c r="B8" s="245" t="s">
         <v>102</v>
       </c>
-      <c r="C8" s="248"/>
-      <c r="D8" s="249" t="str">
+      <c r="C8" s="246"/>
+      <c r="D8" s="261" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_B_SPAT_MTRX</v>
       </c>
-      <c r="E8" s="250"/>
-      <c r="F8" s="250"/>
-      <c r="G8" s="250"/>
-      <c r="H8" s="251"/>
+      <c r="E8" s="262"/>
+      <c r="F8" s="262"/>
+      <c r="G8" s="262"/>
+      <c r="H8" s="263"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="247" t="s">
+      <c r="B9" s="245" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="248"/>
-      <c r="D9" s="252" t="s">
+      <c r="C9" s="246"/>
+      <c r="D9" s="264" t="s">
         <v>274</v>
       </c>
-      <c r="E9" s="253"/>
-      <c r="F9" s="253"/>
-      <c r="G9" s="253"/>
-      <c r="H9" s="254"/>
+      <c r="E9" s="265"/>
+      <c r="F9" s="265"/>
+      <c r="G9" s="265"/>
+      <c r="H9" s="266"/>
     </row>
-    <row r="10" spans="2:14" ht="13.5" thickBot="1">
-      <c r="B10" s="258" t="s">
+    <row r="10" spans="2:14" ht="14.25" thickBot="1">
+      <c r="B10" s="247" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="259"/>
-      <c r="D10" s="255"/>
-      <c r="E10" s="256"/>
-      <c r="F10" s="256"/>
-      <c r="G10" s="256"/>
-      <c r="H10" s="257"/>
+      <c r="C10" s="248"/>
+      <c r="D10" s="267"/>
+      <c r="E10" s="268"/>
+      <c r="F10" s="268"/>
+      <c r="G10" s="268"/>
+      <c r="H10" s="269"/>
     </row>
-    <row r="11" spans="2:14" ht="13.5" thickBot="1"/>
-    <row r="12" spans="2:14" ht="13.5" thickBot="1">
+    <row r="11" spans="2:14" ht="14.25" thickBot="1"/>
+    <row r="12" spans="2:14" ht="14.25" thickBot="1">
       <c r="B12" s="147" t="s">
         <v>39</v>
       </c>
@@ -22862,7 +23065,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="13.5" thickTop="1">
+    <row r="13" spans="2:14" ht="14.25" thickTop="1">
       <c r="B13" s="111">
         <v>1</v>
       </c>
@@ -23715,7 +23918,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="13.5" thickBot="1">
+    <row r="37" spans="2:14" ht="14.25" thickBot="1">
       <c r="B37" s="102">
         <v>25</v>
       </c>
@@ -23756,36 +23959,36 @@
     <protectedRange sqref="D2:H3 D9:H10 C13:E37" name="編集許可"/>
   </protectedRanges>
   <mergeCells count="16">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="D9:H9"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C13:C37">
-    <cfRule type="expression" dxfId="8" priority="4">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>14&lt;LEN($D$6)+LEN($C13)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5">
-    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="NG">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="NG">
       <formula>NOT(ISERROR(SEARCH("NG",D5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="6" priority="3">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>14 &lt; LEN($D$6)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23814,21 +24017,21 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B2:R59"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="36.453125" customWidth="1"/>
-    <col min="6" max="6" width="52.7265625" customWidth="1"/>
-    <col min="7" max="7" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="3.90625" customWidth="1"/>
-    <col min="16" max="16" width="9.90625" customWidth="1"/>
-    <col min="17" max="17" width="44.6328125" customWidth="1"/>
-    <col min="18" max="18" width="73.6328125" customWidth="1"/>
+    <col min="5" max="5" width="36.5" customWidth="1"/>
+    <col min="6" max="6" width="52.75" customWidth="1"/>
+    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="15" width="3.875" customWidth="1"/>
+    <col min="16" max="16" width="9.875" customWidth="1"/>
+    <col min="17" max="17" width="44.625" customWidth="1"/>
+    <col min="18" max="18" width="73.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="13.5" thickBot="1">
+    <row r="2" spans="2:18" ht="14.25" thickBot="1">
       <c r="B2" t="s">
         <v>215</v>
       </c>
@@ -23836,7 +24039,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="13.5" thickBot="1">
+    <row r="3" spans="2:18" ht="14.25" thickBot="1">
       <c r="B3" s="147" t="s">
         <v>39</v>
       </c>
@@ -23868,7 +24071,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="4" spans="2:18" ht="14.25" hidden="1" thickTop="1">
       <c r="B4" s="178">
         <v>0</v>
       </c>
@@ -23890,7 +24093,7 @@
       </c>
       <c r="R4" s="142"/>
     </row>
-    <row r="5" spans="2:18" ht="13.5" thickTop="1">
+    <row r="5" spans="2:18" ht="14.25" thickTop="1">
       <c r="B5" s="181">
         <v>1</v>
       </c>
@@ -24418,7 +24621,7 @@
       <c r="Q28" s="151"/>
       <c r="R28" s="120"/>
     </row>
-    <row r="29" spans="2:18" ht="13.5" thickBot="1">
+    <row r="29" spans="2:18" ht="14.25" thickBot="1">
       <c r="B29" s="182">
         <v>25</v>
       </c>
@@ -24440,7 +24643,7 @@
       <c r="Q29" s="149"/>
       <c r="R29" s="122"/>
     </row>
-    <row r="32" spans="2:18" ht="13.5" thickBot="1">
+    <row r="32" spans="2:18" ht="14.25" thickBot="1">
       <c r="B32" t="s">
         <v>216</v>
       </c>
@@ -24448,7 +24651,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="13.5" thickBot="1">
+    <row r="33" spans="2:18" ht="14.25" thickBot="1">
       <c r="B33" s="147" t="s">
         <v>39</v>
       </c>
@@ -24480,7 +24683,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="34" spans="2:18" ht="14.25" hidden="1" thickTop="1">
       <c r="B34" s="178">
         <v>0</v>
       </c>
@@ -24506,7 +24709,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="13.5" thickTop="1">
+    <row r="35" spans="2:18" ht="14.25" thickTop="1">
       <c r="B35" s="181">
         <v>1</v>
       </c>
@@ -25034,7 +25237,7 @@
       <c r="Q58" s="151"/>
       <c r="R58" s="183"/>
     </row>
-    <row r="59" spans="2:18" ht="13.5" thickBot="1">
+    <row r="59" spans="2:18" ht="14.25" thickBot="1">
       <c r="B59" s="182">
         <v>25</v>
       </c>
@@ -25082,29 +25285,29 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:U103"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="28.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.90625" customWidth="1"/>
-    <col min="5" max="5" width="12.36328125" customWidth="1"/>
-    <col min="6" max="6" width="19.7265625" customWidth="1"/>
-    <col min="7" max="7" width="12.36328125" customWidth="1"/>
+    <col min="2" max="2" width="28.375" customWidth="1"/>
+    <col min="3" max="3" width="15.875" customWidth="1"/>
+    <col min="5" max="5" width="12.375" customWidth="1"/>
+    <col min="6" max="6" width="19.75" customWidth="1"/>
+    <col min="7" max="7" width="12.375" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="12.36328125" customWidth="1"/>
-    <col min="10" max="10" width="31.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.36328125" customWidth="1"/>
-    <col min="12" max="12" width="16.08984375" customWidth="1"/>
-    <col min="14" max="14" width="30.08984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="57.08984375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="12.375" customWidth="1"/>
+    <col min="10" max="10" width="31.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.375" customWidth="1"/>
+    <col min="12" max="12" width="16.125" customWidth="1"/>
+    <col min="14" max="14" width="30.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="57.125" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="13.5" thickBot="1">
+    <row r="1" spans="2:21" ht="14.25" thickBot="1">
       <c r="C1" s="95" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="13.5" thickBot="1">
+    <row r="2" spans="2:21" ht="14.25" thickBot="1">
       <c r="B2" s="103" t="s">
         <v>63</v>
       </c>
@@ -25148,7 +25351,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="14" hidden="1" thickTop="1" thickBot="1">
+    <row r="3" spans="2:21" ht="15" hidden="1" thickTop="1" thickBot="1">
       <c r="B3" s="26"/>
       <c r="C3" s="56" t="s">
         <v>115</v>
@@ -25169,7 +25372,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="13.5" thickTop="1">
+    <row r="4" spans="2:21" ht="14.25" thickTop="1">
       <c r="B4" s="26" t="s">
         <v>247</v>
       </c>
@@ -25437,7 +25640,7 @@
       </c>
       <c r="U12" s="32"/>
     </row>
-    <row r="13" spans="2:21" ht="13.5" thickBot="1">
+    <row r="13" spans="2:21" ht="14.25" thickBot="1">
       <c r="B13" s="26"/>
       <c r="C13" s="25"/>
       <c r="D13" s="119"/>
@@ -27688,7 +27891,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="2:15" ht="13.5" thickBot="1">
+    <row r="103" spans="2:15" ht="14.25" thickBot="1">
       <c r="B103" s="58"/>
       <c r="C103" s="59"/>
       <c r="D103" s="121"/>
@@ -27720,7 +27923,7 @@
   </protectedRanges>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="M3:M103">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
       <formula>32</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27758,18 +27961,18 @@
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
     <col min="4" max="35" width="3" customWidth="1"/>
-    <col min="36" max="36" width="36.36328125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.08984375" customWidth="1"/>
+    <col min="36" max="36" width="36.375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.125" customWidth="1"/>
     <col min="38" max="42" width="9" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="20.6328125" hidden="1" customWidth="1"/>
-    <col min="44" max="47" width="41.08984375" customWidth="1"/>
-    <col min="48" max="48" width="23.6328125" customWidth="1"/>
+    <col min="43" max="43" width="20.625" hidden="1" customWidth="1"/>
+    <col min="44" max="47" width="41.125" customWidth="1"/>
+    <col min="48" max="48" width="23.625" customWidth="1"/>
     <col min="49" max="49" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -27785,7 +27988,7 @@
       <c r="B2" s="127" t="s">
         <v>134</v>
       </c>
-      <c r="C2" s="274" t="s">
+      <c r="C2" s="270" t="s">
         <v>89</v>
       </c>
       <c r="D2" s="63">
@@ -27884,7 +28087,7 @@
       <c r="AI2" s="63">
         <v>0</v>
       </c>
-      <c r="AJ2" s="276" t="s">
+      <c r="AJ2" s="272" t="s">
         <v>167</v>
       </c>
     </row>
@@ -27893,7 +28096,7 @@
         <f>IF(OR(IF(COUNTIF(D6:AC69,"0")&lt;&gt;0,TRUE,FALSE),IF(COUNTIF(D6:AC69,"1")&lt;&gt;0,TRUE,FALSE)),"Search Table","Index Table")</f>
         <v>Index Table</v>
       </c>
-      <c r="C3" s="275"/>
+      <c r="C3" s="271"/>
       <c r="D3" s="129" t="s">
         <v>66</v>
       </c>
@@ -27984,20 +28187,20 @@
       <c r="AG3" s="139" t="s">
         <v>250</v>
       </c>
-      <c r="AH3" s="282" t="s">
+      <c r="AH3" s="278" t="s">
         <v>268</v>
       </c>
-      <c r="AI3" s="283"/>
-      <c r="AJ3" s="277"/>
+      <c r="AI3" s="279"/>
+      <c r="AJ3" s="273"/>
       <c r="AR3" s="96" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="13.5" thickBot="1">
-      <c r="A4" s="278" t="s">
+    <row r="4" spans="1:49" ht="14.25" thickBot="1">
+      <c r="A4" s="274" t="s">
         <v>68</v>
       </c>
-      <c r="B4" s="279"/>
+      <c r="B4" s="275"/>
       <c r="C4" s="137"/>
       <c r="D4" s="137"/>
       <c r="E4" s="137"/>
@@ -28041,9 +28244,9 @@
       <c r="AV4" s="85"/>
       <c r="AW4" s="86"/>
     </row>
-    <row r="5" spans="1:49" ht="13.5" thickBot="1">
-      <c r="A5" s="280"/>
-      <c r="B5" s="281"/>
+    <row r="5" spans="1:49" ht="14.25" thickBot="1">
+      <c r="A5" s="276"/>
+      <c r="B5" s="277"/>
       <c r="C5" s="138"/>
       <c r="D5" s="138"/>
       <c r="E5" s="138"/>
@@ -29552,7 +29755,7 @@
         <v>ALERT_VOM_IGN_ON</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="13.5" thickBot="1">
+    <row r="17" spans="2:49" ht="14.25" thickBot="1">
       <c r="B17" s="134"/>
       <c r="C17" s="52">
         <f t="shared" si="2"/>
@@ -35922,7 +36125,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="13.5" thickBot="1">
+    <row r="70" spans="1:46" ht="14.25" thickBot="1">
       <c r="A70" s="61" t="s">
         <v>69</v>
       </c>
@@ -56514,25 +56717,17 @@
     <mergeCell ref="AH3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="D14:AI69 D6:AF13">
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
+  <conditionalFormatting sqref="D6:AI69">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"×"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AR5:AS70">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>$B$3="Index Table"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG6:AI13">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
-      <formula>"×"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -56556,16 +56751,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B3:AY178"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="35.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="10" width="3.36328125" customWidth="1"/>
+    <col min="2" max="2" width="35.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="3.375" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
-    <col min="12" max="12" width="23.08984375" customWidth="1"/>
-    <col min="13" max="13" width="20.90625" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" customWidth="1"/>
-    <col min="15" max="15" width="31.08984375" customWidth="1"/>
-    <col min="16" max="17" width="10.90625" customWidth="1"/>
+    <col min="12" max="12" width="23.125" customWidth="1"/>
+    <col min="13" max="13" width="20.875" customWidth="1"/>
+    <col min="14" max="14" width="10.875" customWidth="1"/>
+    <col min="15" max="15" width="31.125" customWidth="1"/>
+    <col min="16" max="17" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="21:51">
@@ -56638,25 +56833,25 @@
       <c r="AX91" s="214"/>
       <c r="AY91" s="214"/>
     </row>
-    <row r="101" spans="2:51" ht="14.5" thickBot="1">
+    <row r="101" spans="2:51" ht="15" thickBot="1">
       <c r="B101" s="27" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="102" spans="2:51" ht="14.5" thickBot="1">
+    <row r="102" spans="2:51" ht="15" thickBot="1">
       <c r="B102" s="100" t="s">
         <v>170</v>
       </c>
-      <c r="C102" s="288" t="s">
+      <c r="C102" s="284" t="s">
         <v>264</v>
       </c>
-      <c r="D102" s="289"/>
-      <c r="E102" s="289"/>
-      <c r="F102" s="289"/>
-      <c r="G102" s="289"/>
-      <c r="H102" s="289"/>
-      <c r="I102" s="289"/>
-      <c r="J102" s="290"/>
+      <c r="D102" s="285"/>
+      <c r="E102" s="285"/>
+      <c r="F102" s="285"/>
+      <c r="G102" s="285"/>
+      <c r="H102" s="285"/>
+      <c r="I102" s="285"/>
+      <c r="J102" s="286"/>
       <c r="K102" s="174"/>
       <c r="L102" s="174"/>
       <c r="M102" s="177"/>
@@ -56726,16 +56921,16 @@
       <c r="B104" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="C104" s="284" t="s">
+      <c r="C104" s="280" t="s">
         <v>192</v>
       </c>
-      <c r="D104" s="285"/>
-      <c r="E104" s="285"/>
-      <c r="F104" s="285"/>
-      <c r="G104" s="285"/>
-      <c r="H104" s="285"/>
-      <c r="I104" s="285"/>
-      <c r="J104" s="286"/>
+      <c r="D104" s="281"/>
+      <c r="E104" s="281"/>
+      <c r="F104" s="281"/>
+      <c r="G104" s="281"/>
+      <c r="H104" s="281"/>
+      <c r="I104" s="281"/>
+      <c r="J104" s="282"/>
       <c r="K104" s="29" t="s">
         <v>23</v>
       </c>
@@ -56798,20 +56993,20 @@
       <c r="P105" s="81"/>
       <c r="Q105" s="142"/>
     </row>
-    <row r="106" spans="2:51" ht="26">
+    <row r="106" spans="2:51" ht="27">
       <c r="B106" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="C106" s="287" t="s">
+      <c r="C106" s="283" t="s">
         <v>174</v>
       </c>
-      <c r="D106" s="285"/>
-      <c r="E106" s="285"/>
-      <c r="F106" s="285"/>
-      <c r="G106" s="285"/>
-      <c r="H106" s="285"/>
-      <c r="I106" s="285"/>
-      <c r="J106" s="286"/>
+      <c r="D106" s="281"/>
+      <c r="E106" s="281"/>
+      <c r="F106" s="281"/>
+      <c r="G106" s="281"/>
+      <c r="H106" s="281"/>
+      <c r="I106" s="281"/>
+      <c r="J106" s="282"/>
       <c r="K106" s="1" t="s">
         <v>256</v>
       </c>
@@ -56824,7 +57019,7 @@
       <c r="P106" s="81"/>
       <c r="Q106" s="142"/>
     </row>
-    <row r="107" spans="2:51" ht="131">
+    <row r="107" spans="2:51" ht="136.5">
       <c r="B107" s="74" t="s">
         <v>29</v>
       </c>
@@ -56866,7 +57061,7 @@
       <c r="P107" s="81"/>
       <c r="Q107" s="142"/>
     </row>
-    <row r="108" spans="2:51" ht="39.5" thickBot="1">
+    <row r="108" spans="2:51" ht="41.25" thickBot="1">
       <c r="B108" s="76" t="s">
         <v>31</v>
       </c>
@@ -56910,7 +57105,7 @@
       <c r="P108" s="79"/>
       <c r="Q108" s="143"/>
     </row>
-    <row r="109" spans="2:51" ht="13.5" thickTop="1">
+    <row r="109" spans="2:51" ht="14.25" thickTop="1">
       <c r="B109" s="77" t="s">
         <v>271</v>
       </c>
@@ -57130,7 +57325,7 @@
       <c r="P113" s="47"/>
       <c r="Q113" s="145"/>
     </row>
-    <row r="114" spans="2:17" ht="13.5" thickBot="1">
+    <row r="114" spans="2:17" ht="14.25" thickBot="1">
       <c r="B114" s="23" t="s">
         <v>261</v>
       </c>
@@ -57266,14 +57461,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:D27"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="4.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.26953125" customWidth="1"/>
+    <col min="2" max="2" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.25" customWidth="1"/>
     <col min="4" max="4" width="86" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="13.5" thickBot="1">
+    <row r="2" spans="2:4" ht="14.25" thickBot="1">
       <c r="B2" s="88" t="s">
         <v>92</v>
       </c>
@@ -57283,7 +57478,7 @@
       </c>
       <c r="D2" s="89"/>
     </row>
-    <row r="3" spans="2:4" ht="13.5" thickBot="1">
+    <row r="3" spans="2:4" ht="14.25" thickBot="1">
       <c r="B3" s="82" t="s">
         <v>90</v>
       </c>
@@ -57294,7 +57489,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="13.5" thickTop="1">
+    <row r="4" spans="2:4" ht="14.25" thickTop="1">
       <c r="B4" s="13">
         <v>0</v>
       </c>
@@ -57305,7 +57500,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="39">
+    <row r="5" spans="2:4" ht="40.5">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -57316,7 +57511,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="26">
+    <row r="6" spans="2:4" ht="27">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -57327,7 +57522,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="52">
+    <row r="7" spans="2:4" ht="54">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -57338,7 +57533,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="78">
+    <row r="8" spans="2:4" ht="81">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -57360,7 +57555,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="26">
+    <row r="10" spans="2:4" ht="27">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -57371,7 +57566,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="26">
+    <row r="11" spans="2:4" ht="27">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -57382,7 +57577,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="26">
+    <row r="12" spans="2:4" ht="27">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -57393,7 +57588,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="26">
+    <row r="13" spans="2:4" ht="27">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -57404,7 +57599,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="26">
+    <row r="14" spans="2:4" ht="27">
       <c r="B14" s="2">
         <v>10</v>
       </c>
@@ -57415,7 +57610,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="130">
+    <row r="15" spans="2:4" ht="135">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -57437,7 +57632,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="26">
+    <row r="17" spans="2:4" ht="27">
       <c r="B17" s="2">
         <v>13</v>
       </c>
@@ -57448,7 +57643,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="91">
+    <row r="18" spans="2:4" ht="67.5">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -57459,7 +57654,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="39">
+    <row r="19" spans="2:4" ht="40.5">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -57492,7 +57687,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="26">
+    <row r="22" spans="2:4" ht="27">
       <c r="B22" s="2">
         <v>18</v>
       </c>
@@ -57503,7 +57698,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="26">
+    <row r="23" spans="2:4" ht="27">
       <c r="B23" s="2">
         <v>19</v>
       </c>
@@ -57514,7 +57709,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="24" spans="2:4" ht="91">
+    <row r="24" spans="2:4" ht="94.5">
       <c r="B24" s="2">
         <v>20</v>
       </c>
@@ -57535,7 +57730,7 @@
       <c r="C26" s="92"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="2:4" ht="13.5" thickBot="1">
+    <row r="27" spans="2:4" ht="14.25" thickBot="1">
       <c r="B27" s="4"/>
       <c r="C27" s="93"/>
       <c r="D27" s="6"/>
